--- a/tests/output/20260218response_small_all.xlsx
+++ b/tests/output/20260218response_small_all.xlsx
@@ -49,30 +49,30 @@
     <t>g00576</t>
   </si>
   <si>
+    <t>a00213</t>
+  </si>
+  <si>
+    <t>a00221</t>
+  </si>
+  <si>
+    <t>a00203</t>
+  </si>
+  <si>
     <t>a00216</t>
   </si>
   <si>
     <t>a00205</t>
   </si>
   <si>
-    <t>a00203</t>
-  </si>
-  <si>
-    <t>a00221</t>
-  </si>
-  <si>
-    <t>a00213</t>
-  </si>
-  <si>
     <t>a00220</t>
   </si>
   <si>
+    <t>a00217</t>
+  </si>
+  <si>
     <t>a00212</t>
   </si>
   <si>
-    <t>a00217</t>
-  </si>
-  <si>
     <t>a00219</t>
   </si>
   <si>
@@ -91,216 +91,216 @@
     <t>a00214</t>
   </si>
   <si>
+    <t>t00140</t>
+  </si>
+  <si>
+    <t>t00260</t>
+  </si>
+  <si>
+    <t>t00059</t>
+  </si>
+  <si>
     <t>t00181</t>
   </si>
   <si>
     <t>t00043</t>
   </si>
   <si>
-    <t>t00059</t>
-  </si>
-  <si>
-    <t>t00260</t>
-  </si>
-  <si>
-    <t>t00140</t>
+    <t>t00142</t>
+  </si>
+  <si>
+    <t>t00262</t>
+  </si>
+  <si>
+    <t>t00060</t>
+  </si>
+  <si>
+    <t>t00183</t>
   </si>
   <si>
     <t>t00044</t>
   </si>
   <si>
-    <t>t00060</t>
-  </si>
-  <si>
-    <t>t00262</t>
-  </si>
-  <si>
-    <t>t00142</t>
-  </si>
-  <si>
-    <t>t00183</t>
+    <t>t00185</t>
+  </si>
+  <si>
+    <t>t00144</t>
   </si>
   <si>
     <t>t00264</t>
   </si>
   <si>
-    <t>t00144</t>
-  </si>
-  <si>
-    <t>t00185</t>
-  </si>
-  <si>
     <t>t00256</t>
   </si>
   <si>
+    <t>t00187</t>
+  </si>
+  <si>
+    <t>t00219</t>
+  </si>
+  <si>
+    <t>t00266</t>
+  </si>
+  <si>
+    <t>t00146</t>
+  </si>
+  <si>
     <t>t00132</t>
   </si>
   <si>
-    <t>t00187</t>
-  </si>
-  <si>
-    <t>t00146</t>
-  </si>
-  <si>
-    <t>t00219</t>
-  </si>
-  <si>
-    <t>t00266</t>
+    <t>t00268</t>
+  </si>
+  <si>
+    <t>t00246</t>
+  </si>
+  <si>
+    <t>t00189</t>
+  </si>
+  <si>
+    <t>t00133</t>
   </si>
   <si>
     <t>t00220</t>
   </si>
   <si>
-    <t>t00268</t>
-  </si>
-  <si>
-    <t>t00246</t>
-  </si>
-  <si>
-    <t>t00133</t>
-  </si>
-  <si>
-    <t>t00189</t>
-  </si>
-  <si>
     <t>t00247</t>
   </si>
   <si>
+    <t>t00045</t>
+  </si>
+  <si>
+    <t>t00270</t>
+  </si>
+  <si>
+    <t>t00148</t>
+  </si>
+  <si>
+    <t>t00115</t>
+  </si>
+  <si>
     <t>t00191</t>
   </si>
   <si>
-    <t>t00148</t>
-  </si>
-  <si>
-    <t>t00045</t>
-  </si>
-  <si>
-    <t>t00270</t>
-  </si>
-  <si>
-    <t>t00115</t>
-  </si>
-  <si>
     <t>t00257</t>
   </si>
   <si>
+    <t>t00193</t>
+  </si>
+  <si>
+    <t>t00221</t>
+  </si>
+  <si>
+    <t>t00046</t>
+  </si>
+  <si>
+    <t>t00150</t>
+  </si>
+  <si>
+    <t>t00116</t>
+  </si>
+  <si>
+    <t>t00134</t>
+  </si>
+  <si>
     <t>t00272</t>
   </si>
   <si>
-    <t>t00150</t>
-  </si>
-  <si>
-    <t>t00221</t>
-  </si>
-  <si>
-    <t>t00193</t>
-  </si>
-  <si>
-    <t>t00046</t>
-  </si>
-  <si>
-    <t>t00116</t>
-  </si>
-  <si>
-    <t>t00134</t>
+    <t>t00135</t>
+  </si>
+  <si>
+    <t>t00274</t>
+  </si>
+  <si>
+    <t>t00222</t>
   </si>
   <si>
     <t>t00195</t>
   </si>
   <si>
-    <t>t00135</t>
-  </si>
-  <si>
-    <t>t00274</t>
-  </si>
-  <si>
-    <t>t00222</t>
-  </si>
-  <si>
     <t>t00248</t>
   </si>
   <si>
     <t>t00249</t>
   </si>
   <si>
+    <t>t00276</t>
+  </si>
+  <si>
+    <t>t00117</t>
+  </si>
+  <si>
     <t>t00061</t>
   </si>
   <si>
-    <t>t00276</t>
-  </si>
-  <si>
-    <t>t00117</t>
-  </si>
-  <si>
     <t>t00197</t>
   </si>
   <si>
     <t>t00047</t>
   </si>
   <si>
+    <t>t00048</t>
+  </si>
+  <si>
+    <t>t00223</t>
+  </si>
+  <si>
+    <t>t00278</t>
+  </si>
+  <si>
+    <t>t00118</t>
+  </si>
+  <si>
     <t>t00136</t>
   </si>
   <si>
+    <t>t00062</t>
+  </si>
+  <si>
     <t>t00199</t>
   </si>
   <si>
-    <t>t00048</t>
-  </si>
-  <si>
-    <t>t00223</t>
-  </si>
-  <si>
-    <t>t00062</t>
-  </si>
-  <si>
-    <t>t00278</t>
-  </si>
-  <si>
-    <t>t00118</t>
+    <t>t00224</t>
+  </si>
+  <si>
+    <t>t00137</t>
+  </si>
+  <si>
+    <t>t00280</t>
+  </si>
+  <si>
+    <t>t00250</t>
   </si>
   <si>
     <t>t00201</t>
   </si>
   <si>
-    <t>t00224</t>
-  </si>
-  <si>
-    <t>t00137</t>
-  </si>
-  <si>
-    <t>t00280</t>
-  </si>
-  <si>
-    <t>t00250</t>
-  </si>
-  <si>
     <t>t00251</t>
   </si>
   <si>
+    <t>t00282</t>
+  </si>
+  <si>
+    <t>t00063</t>
+  </si>
+  <si>
     <t>t00203</t>
   </si>
   <si>
-    <t>t00063</t>
-  </si>
-  <si>
-    <t>t00282</t>
-  </si>
-  <si>
     <t>t00258</t>
   </si>
   <si>
     <t>t00225</t>
   </si>
   <si>
+    <t>t00284</t>
+  </si>
+  <si>
+    <t>t00138</t>
+  </si>
+  <si>
     <t>t00064</t>
   </si>
   <si>
-    <t>t00284</t>
-  </si>
-  <si>
-    <t>t00138</t>
-  </si>
-  <si>
     <t>t00205</t>
   </si>
   <si>
@@ -316,93 +316,93 @@
     <t>t00253</t>
   </si>
   <si>
+    <t>t00288</t>
+  </si>
+  <si>
+    <t>t00065</t>
+  </si>
+  <si>
+    <t>t00209</t>
+  </si>
+  <si>
     <t>t00049</t>
   </si>
   <si>
-    <t>t00065</t>
-  </si>
-  <si>
-    <t>t00288</t>
-  </si>
-  <si>
     <t>t00152</t>
   </si>
   <si>
-    <t>t00209</t>
-  </si>
-  <si>
     <t>t00259</t>
   </si>
   <si>
+    <t>t00290</t>
+  </si>
+  <si>
+    <t>t00066</t>
+  </si>
+  <si>
+    <t>t00211</t>
+  </si>
+  <si>
+    <t>t00050</t>
+  </si>
+  <si>
+    <t>t00154</t>
+  </si>
+  <si>
+    <t>t00226</t>
+  </si>
+  <si>
     <t>t00139</t>
   </si>
   <si>
-    <t>t00066</t>
-  </si>
-  <si>
-    <t>t00290</t>
-  </si>
-  <si>
-    <t>t00154</t>
-  </si>
-  <si>
-    <t>t00211</t>
-  </si>
-  <si>
-    <t>t00050</t>
-  </si>
-  <si>
-    <t>t00226</t>
+    <t>t00213</t>
+  </si>
+  <si>
+    <t>t00254</t>
   </si>
   <si>
     <t>t00292</t>
   </si>
   <si>
-    <t>t00213</t>
-  </si>
-  <si>
-    <t>t00254</t>
-  </si>
-  <si>
     <t>t00255</t>
   </si>
   <si>
+    <t>t00215</t>
+  </si>
+  <si>
+    <t>t00051</t>
+  </si>
+  <si>
+    <t>t00156</t>
+  </si>
+  <si>
+    <t>t00294</t>
+  </si>
+  <si>
     <t>t00119</t>
   </si>
   <si>
-    <t>t00294</t>
-  </si>
-  <si>
-    <t>t00156</t>
-  </si>
-  <si>
-    <t>t00215</t>
-  </si>
-  <si>
-    <t>t00051</t>
-  </si>
-  <si>
     <t>t00067</t>
   </si>
   <si>
+    <t>t00217</t>
+  </si>
+  <si>
+    <t>t00052</t>
+  </si>
+  <si>
+    <t>t00158</t>
+  </si>
+  <si>
+    <t>t00296</t>
+  </si>
+  <si>
     <t>t00120</t>
   </si>
   <si>
-    <t>t00158</t>
-  </si>
-  <si>
-    <t>t00217</t>
-  </si>
-  <si>
-    <t>t00052</t>
-  </si>
-  <si>
     <t>t00068</t>
   </si>
   <si>
-    <t>t00296</t>
-  </si>
-  <si>
     <t>t00227</t>
   </si>
   <si>
@@ -418,15 +418,15 @@
     <t>t00230</t>
   </si>
   <si>
+    <t>t00231</t>
+  </si>
+  <si>
     <t>t00167</t>
   </si>
   <si>
     <t>t00075</t>
   </si>
   <si>
-    <t>t00231</t>
-  </si>
-  <si>
     <t>t00160</t>
   </si>
   <si>
@@ -442,52 +442,55 @@
     <t>t00233</t>
   </si>
   <si>
+    <t>t00234</t>
+  </si>
+  <si>
+    <t>t00171</t>
+  </si>
+  <si>
     <t>t00077</t>
   </si>
   <si>
-    <t>t00171</t>
-  </si>
-  <si>
     <t>t00161</t>
   </si>
   <si>
-    <t>t00234</t>
-  </si>
-  <si>
     <t>t00078</t>
   </si>
   <si>
     <t>t00235</t>
   </si>
   <si>
+    <t>t00236</t>
+  </si>
+  <si>
     <t>t00173</t>
   </si>
   <si>
-    <t>t00236</t>
+    <t>t00079</t>
+  </si>
+  <si>
+    <t>t00162</t>
+  </si>
+  <si>
+    <t>t00237</t>
   </si>
   <si>
     <t>t00175</t>
   </si>
   <si>
-    <t>t00079</t>
-  </si>
-  <si>
-    <t>t00162</t>
-  </si>
-  <si>
-    <t>t00237</t>
-  </si>
-  <si>
     <t>t00080</t>
   </si>
   <si>
     <t>t00238</t>
   </si>
   <si>
+    <t>t00239</t>
+  </si>
+  <si>
     <t>t00177</t>
   </si>
   <si>
-    <t>t00239</t>
+    <t>t00081</t>
   </si>
   <si>
     <t>t00163</t>
@@ -496,21 +499,18 @@
     <t>t00240</t>
   </si>
   <si>
-    <t>t00081</t>
-  </si>
-  <si>
     <t>t00082</t>
   </si>
   <si>
     <t>t00241</t>
   </si>
   <si>
+    <t>t00179</t>
+  </si>
+  <si>
     <t>t00242</t>
   </si>
   <si>
-    <t>t00179</t>
-  </si>
-  <si>
     <t>t00083</t>
   </si>
   <si>
@@ -529,16 +529,16 @@
     <t>t00245</t>
   </si>
   <si>
+    <t>veddelev</t>
+  </si>
+  <si>
+    <t>hoje-taastrup</t>
+  </si>
+  <si>
+    <t>lejren</t>
+  </si>
+  <si>
     <t>roskilde</t>
-  </si>
-  <si>
-    <t>lejren</t>
-  </si>
-  <si>
-    <t>hoje-taastrup</t>
-  </si>
-  <si>
-    <t>veddelev</t>
   </si>
   <si>
     <t>ruc</t>
@@ -949,16 +949,16 @@
         <v>46222.29166666666</v>
       </c>
       <c r="E2" s="2">
-        <v>46222.41666666666</v>
+        <v>46222.39583333334</v>
       </c>
       <c r="F2" t="s">
         <v>171</v>
       </c>
       <c r="G2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -978,16 +978,16 @@
         <v>46222.29166666666</v>
       </c>
       <c r="E3" s="2">
-        <v>46222.39583333334</v>
+        <v>46222.41666666666</v>
       </c>
       <c r="F3" t="s">
         <v>172</v>
       </c>
       <c r="G3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1010,7 +1010,7 @@
         <v>46222.35416666666</v>
       </c>
       <c r="F4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G4">
         <v>10</v>
@@ -1039,16 +1039,16 @@
         <v>46222.41666666666</v>
       </c>
       <c r="F5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G5">
+        <v>7</v>
+      </c>
+      <c r="H5">
+        <v>14</v>
+      </c>
+      <c r="I5">
         <v>1</v>
-      </c>
-      <c r="H5">
-        <v>20</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -1068,13 +1068,13 @@
         <v>46222.39583333334</v>
       </c>
       <c r="F6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H6">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1085,7 +1085,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
         <v>30</v>
@@ -1097,16 +1097,16 @@
         <v>46222.58333333334</v>
       </c>
       <c r="F7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G7">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H7">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -1114,7 +1114,7 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" t="s">
         <v>31</v>
@@ -1123,16 +1123,16 @@
         <v>46222.47916666666</v>
       </c>
       <c r="E8" s="2">
-        <v>46222.54166666666</v>
+        <v>46222.60416666666</v>
       </c>
       <c r="F8" t="s">
         <v>172</v>
       </c>
       <c r="G8">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H8">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -1143,7 +1143,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
         <v>32</v>
@@ -1152,16 +1152,16 @@
         <v>46222.47916666666</v>
       </c>
       <c r="E9" s="2">
-        <v>46222.60416666666</v>
+        <v>46222.54166666666</v>
       </c>
       <c r="F9" t="s">
         <v>173</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H9">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -1172,7 +1172,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
         <v>33</v>
@@ -1181,16 +1181,16 @@
         <v>46222.47916666666</v>
       </c>
       <c r="E10" s="2">
-        <v>46222.58333333334</v>
+        <v>46222.60416666666</v>
       </c>
       <c r="F10" t="s">
         <v>174</v>
       </c>
       <c r="G10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H10">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -1201,7 +1201,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
         <v>34</v>
@@ -1210,16 +1210,16 @@
         <v>46222.47916666666</v>
       </c>
       <c r="E11" s="2">
-        <v>46222.60416666666</v>
+        <v>46222.58333333334</v>
       </c>
       <c r="F11" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G11">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H11">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -1242,13 +1242,13 @@
         <v>46223.41666666666</v>
       </c>
       <c r="F12" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H12">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -1259,7 +1259,7 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C13" t="s">
         <v>36</v>
@@ -1271,7 +1271,7 @@
         <v>46223.39583333334</v>
       </c>
       <c r="F13" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -1288,7 +1288,7 @@
         <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C14" t="s">
         <v>37</v>
@@ -1300,13 +1300,13 @@
         <v>46223.41666666666</v>
       </c>
       <c r="F14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G14">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H14">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -1346,7 +1346,7 @@
         <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C16" t="s">
         <v>39</v>
@@ -1355,16 +1355,16 @@
         <v>46223.47916666666</v>
       </c>
       <c r="E16" s="2">
-        <v>46223.5625</v>
+        <v>46223.60416666666</v>
       </c>
       <c r="F16" t="s">
         <v>174</v>
       </c>
       <c r="G16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H16">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -1375,7 +1375,7 @@
         <v>9</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C17" t="s">
         <v>40</v>
@@ -1384,16 +1384,16 @@
         <v>46223.47916666666</v>
       </c>
       <c r="E17" s="2">
-        <v>46223.60416666666</v>
+        <v>46223.54166666666</v>
       </c>
       <c r="F17" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H17">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1404,7 +1404,7 @@
         <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C18" t="s">
         <v>41</v>
@@ -1413,16 +1413,16 @@
         <v>46223.47916666666</v>
       </c>
       <c r="E18" s="2">
-        <v>46223.58333333334</v>
+        <v>46223.60416666666</v>
       </c>
       <c r="F18" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G18">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1433,7 +1433,7 @@
         <v>9</v>
       </c>
       <c r="B19" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C19" t="s">
         <v>42</v>
@@ -1442,16 +1442,16 @@
         <v>46223.47916666666</v>
       </c>
       <c r="E19" s="2">
-        <v>46223.54166666666</v>
+        <v>46223.58333333334</v>
       </c>
       <c r="F19" t="s">
         <v>171</v>
       </c>
       <c r="G19">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H19">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -1462,7 +1462,7 @@
         <v>9</v>
       </c>
       <c r="B20" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C20" t="s">
         <v>43</v>
@@ -1471,16 +1471,16 @@
         <v>46223.47916666666</v>
       </c>
       <c r="E20" s="2">
-        <v>46223.60416666666</v>
+        <v>46223.5625</v>
       </c>
       <c r="F20" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G20">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H20">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -1491,7 +1491,7 @@
         <v>9</v>
       </c>
       <c r="B21" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C21" t="s">
         <v>44</v>
@@ -1500,16 +1500,16 @@
         <v>46223.70833333334</v>
       </c>
       <c r="E21" s="2">
-        <v>46223.77083333334</v>
+        <v>46223.83333333334</v>
       </c>
       <c r="F21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G21">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H21">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -1520,7 +1520,7 @@
         <v>9</v>
       </c>
       <c r="B22" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C22" t="s">
         <v>45</v>
@@ -1529,16 +1529,16 @@
         <v>46223.70833333334</v>
       </c>
       <c r="E22" s="2">
-        <v>46223.83333333334</v>
+        <v>46223.77083333334</v>
       </c>
       <c r="F22" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G22">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H22">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -1549,7 +1549,7 @@
         <v>9</v>
       </c>
       <c r="B23" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C23" t="s">
         <v>46</v>
@@ -1558,16 +1558,16 @@
         <v>46223.70833333334</v>
       </c>
       <c r="E23" s="2">
-        <v>46223.77083333334</v>
+        <v>46223.83333333334</v>
       </c>
       <c r="F23" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G23">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H23">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -1578,7 +1578,7 @@
         <v>9</v>
       </c>
       <c r="B24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C24" t="s">
         <v>47</v>
@@ -1590,7 +1590,7 @@
         <v>46223.79166666666</v>
       </c>
       <c r="F24" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G24">
         <v>6</v>
@@ -1607,7 +1607,7 @@
         <v>9</v>
       </c>
       <c r="B25" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C25" t="s">
         <v>48</v>
@@ -1616,16 +1616,16 @@
         <v>46223.70833333334</v>
       </c>
       <c r="E25" s="2">
-        <v>46223.83333333334</v>
+        <v>46223.77083333334</v>
       </c>
       <c r="F25" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H25">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -1648,7 +1648,7 @@
         <v>46223.83333333334</v>
       </c>
       <c r="F26" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G26">
         <v>4</v>
@@ -1665,7 +1665,7 @@
         <v>9</v>
       </c>
       <c r="B27" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C27" t="s">
         <v>50</v>
@@ -1674,16 +1674,16 @@
         <v>46224.29166666666</v>
       </c>
       <c r="E27" s="2">
-        <v>46224.41666666666</v>
+        <v>46224.39583333334</v>
       </c>
       <c r="F27" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G27">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H27">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -1694,7 +1694,7 @@
         <v>9</v>
       </c>
       <c r="B28" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C28" t="s">
         <v>51</v>
@@ -1703,16 +1703,16 @@
         <v>46224.29166666666</v>
       </c>
       <c r="E28" s="2">
-        <v>46224.39583333334</v>
+        <v>46224.41666666666</v>
       </c>
       <c r="F28" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G28">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H28">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -1723,7 +1723,7 @@
         <v>9</v>
       </c>
       <c r="B29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C29" t="s">
         <v>52</v>
@@ -1735,13 +1735,13 @@
         <v>46224.39583333334</v>
       </c>
       <c r="F29" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G29">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H29">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -1752,7 +1752,7 @@
         <v>9</v>
       </c>
       <c r="B30" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C30" t="s">
         <v>53</v>
@@ -1761,16 +1761,16 @@
         <v>46224.29166666666</v>
       </c>
       <c r="E30" s="2">
-        <v>46224.41666666666</v>
+        <v>46224.375</v>
       </c>
       <c r="F30" t="s">
         <v>173</v>
       </c>
       <c r="G30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H30">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -1781,7 +1781,7 @@
         <v>9</v>
       </c>
       <c r="B31" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C31" t="s">
         <v>54</v>
@@ -1790,16 +1790,16 @@
         <v>46224.29166666666</v>
       </c>
       <c r="E31" s="2">
-        <v>46224.375</v>
+        <v>46224.41666666666</v>
       </c>
       <c r="F31" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G31">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H31">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -1851,13 +1851,13 @@
         <v>46224.60416666666</v>
       </c>
       <c r="F33" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G33">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H33">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -1868,7 +1868,7 @@
         <v>9</v>
       </c>
       <c r="B34" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C34" t="s">
         <v>57</v>
@@ -1877,19 +1877,19 @@
         <v>46224.47916666666</v>
       </c>
       <c r="E34" s="2">
-        <v>46224.58333333334</v>
+        <v>46224.54166666666</v>
       </c>
       <c r="F34" t="s">
         <v>174</v>
       </c>
       <c r="G34">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H34">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I34">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1897,7 +1897,7 @@
         <v>9</v>
       </c>
       <c r="B35" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C35" t="s">
         <v>58</v>
@@ -1906,16 +1906,16 @@
         <v>46224.47916666666</v>
       </c>
       <c r="E35" s="2">
-        <v>46224.54166666666</v>
+        <v>46224.58333333334</v>
       </c>
       <c r="F35" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H35">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -1935,16 +1935,16 @@
         <v>46224.47916666666</v>
       </c>
       <c r="E36" s="2">
-        <v>46224.60416666666</v>
+        <v>46224.58333333334</v>
       </c>
       <c r="F36" t="s">
         <v>171</v>
       </c>
       <c r="G36">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H36">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>9</v>
       </c>
       <c r="B37" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C37" t="s">
         <v>60</v>
@@ -1964,16 +1964,16 @@
         <v>46224.47916666666</v>
       </c>
       <c r="E37" s="2">
-        <v>46224.58333333334</v>
+        <v>46224.5625</v>
       </c>
       <c r="F37" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G37">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H37">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -1984,7 +1984,7 @@
         <v>9</v>
       </c>
       <c r="B38" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C38" t="s">
         <v>61</v>
@@ -1996,13 +1996,13 @@
         <v>46224.5625</v>
       </c>
       <c r="F38" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G38">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H38">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -2013,7 +2013,7 @@
         <v>9</v>
       </c>
       <c r="B39" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C39" t="s">
         <v>62</v>
@@ -2022,16 +2022,16 @@
         <v>46224.47916666666</v>
       </c>
       <c r="E39" s="2">
-        <v>46224.5625</v>
+        <v>46224.60416666666</v>
       </c>
       <c r="F39" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G39">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H39">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -2042,7 +2042,7 @@
         <v>9</v>
       </c>
       <c r="B40" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C40" t="s">
         <v>63</v>
@@ -2051,16 +2051,16 @@
         <v>46224.70833333334</v>
       </c>
       <c r="E40" s="2">
-        <v>46224.83333333334</v>
+        <v>46224.79166666666</v>
       </c>
       <c r="F40" t="s">
         <v>171</v>
       </c>
       <c r="G40">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H40">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -2071,7 +2071,7 @@
         <v>9</v>
       </c>
       <c r="B41" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C41" t="s">
         <v>64</v>
@@ -2080,16 +2080,16 @@
         <v>46224.70833333334</v>
       </c>
       <c r="E41" s="2">
-        <v>46224.79166666666</v>
+        <v>46224.83333333334</v>
       </c>
       <c r="F41" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G41">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H41">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -2100,7 +2100,7 @@
         <v>9</v>
       </c>
       <c r="B42" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C42" t="s">
         <v>65</v>
@@ -2109,16 +2109,16 @@
         <v>46224.70833333334</v>
       </c>
       <c r="E42" s="2">
-        <v>46224.83333333334</v>
+        <v>46224.77083333334</v>
       </c>
       <c r="F42" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G42">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H42">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -2129,7 +2129,7 @@
         <v>9</v>
       </c>
       <c r="B43" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C43" t="s">
         <v>66</v>
@@ -2138,16 +2138,16 @@
         <v>46224.70833333334</v>
       </c>
       <c r="E43" s="2">
-        <v>46224.77083333334</v>
+        <v>46224.83333333334</v>
       </c>
       <c r="F43" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G43">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H43">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -2170,7 +2170,7 @@
         <v>46224.75</v>
       </c>
       <c r="F44" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G44">
         <v>4</v>
@@ -2199,7 +2199,7 @@
         <v>46224.83333333334</v>
       </c>
       <c r="F45" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G45">
         <v>4</v>
@@ -2208,7 +2208,7 @@
         <v>17</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -2216,7 +2216,7 @@
         <v>9</v>
       </c>
       <c r="B46" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C46" t="s">
         <v>69</v>
@@ -2225,16 +2225,16 @@
         <v>46225.29166666666</v>
       </c>
       <c r="E46" s="2">
-        <v>46225.35416666666</v>
+        <v>46225.41666666666</v>
       </c>
       <c r="F46" t="s">
         <v>172</v>
       </c>
       <c r="G46">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H46">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -2245,7 +2245,7 @@
         <v>9</v>
       </c>
       <c r="B47" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C47" t="s">
         <v>70</v>
@@ -2254,19 +2254,19 @@
         <v>46225.29166666666</v>
       </c>
       <c r="E47" s="2">
-        <v>46225.41666666666</v>
+        <v>46225.375</v>
       </c>
       <c r="F47" t="s">
         <v>173</v>
       </c>
       <c r="G47">
+        <v>3</v>
+      </c>
+      <c r="H47">
+        <v>18</v>
+      </c>
+      <c r="I47">
         <v>1</v>
-      </c>
-      <c r="H47">
-        <v>20</v>
-      </c>
-      <c r="I47">
-        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -2274,7 +2274,7 @@
         <v>9</v>
       </c>
       <c r="B48" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C48" t="s">
         <v>71</v>
@@ -2283,16 +2283,16 @@
         <v>46225.29166666666</v>
       </c>
       <c r="E48" s="2">
-        <v>46225.375</v>
+        <v>46225.35416666666</v>
       </c>
       <c r="F48" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G48">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H48">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -2303,7 +2303,7 @@
         <v>9</v>
       </c>
       <c r="B49" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C49" t="s">
         <v>72</v>
@@ -2315,7 +2315,7 @@
         <v>46225.41666666666</v>
       </c>
       <c r="F49" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G49">
         <v>7</v>
@@ -2332,7 +2332,7 @@
         <v>9</v>
       </c>
       <c r="B50" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C50" t="s">
         <v>73</v>
@@ -2344,7 +2344,7 @@
         <v>46225.39583333334</v>
       </c>
       <c r="F50" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G50">
         <v>9</v>
@@ -2361,7 +2361,7 @@
         <v>9</v>
       </c>
       <c r="B51" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C51" t="s">
         <v>74</v>
@@ -2370,19 +2370,19 @@
         <v>46225.47916666666</v>
       </c>
       <c r="E51" s="2">
-        <v>46225.5625</v>
+        <v>46225.58333333334</v>
       </c>
       <c r="F51" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G51">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H51">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I51">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -2390,7 +2390,7 @@
         <v>9</v>
       </c>
       <c r="B52" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C52" t="s">
         <v>75</v>
@@ -2399,19 +2399,19 @@
         <v>46225.47916666666</v>
       </c>
       <c r="E52" s="2">
-        <v>46225.60416666666</v>
+        <v>46225.54166666666</v>
       </c>
       <c r="F52" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G52">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H52">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I52">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -2428,16 +2428,16 @@
         <v>46225.47916666666</v>
       </c>
       <c r="E53" s="2">
-        <v>46225.58333333334</v>
+        <v>46225.60416666666</v>
       </c>
       <c r="F53" t="s">
         <v>172</v>
       </c>
       <c r="G53">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H53">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -2448,7 +2448,7 @@
         <v>9</v>
       </c>
       <c r="B54" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C54" t="s">
         <v>77</v>
@@ -2457,16 +2457,16 @@
         <v>46225.47916666666</v>
       </c>
       <c r="E54" s="2">
-        <v>46225.54166666666</v>
+        <v>46225.5625</v>
       </c>
       <c r="F54" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G54">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H54">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -2477,7 +2477,7 @@
         <v>9</v>
       </c>
       <c r="B55" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C55" t="s">
         <v>78</v>
@@ -2486,16 +2486,16 @@
         <v>46225.47916666666</v>
       </c>
       <c r="E55" s="2">
-        <v>46225.54166666666</v>
+        <v>46225.5625</v>
       </c>
       <c r="F55" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G55">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H55">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -2506,7 +2506,7 @@
         <v>9</v>
       </c>
       <c r="B56" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C56" t="s">
         <v>79</v>
@@ -2515,16 +2515,16 @@
         <v>46225.47916666666</v>
       </c>
       <c r="E56" s="2">
-        <v>46225.60416666666</v>
+        <v>46225.54166666666</v>
       </c>
       <c r="F56" t="s">
         <v>173</v>
       </c>
       <c r="G56">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H56">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -2535,7 +2535,7 @@
         <v>9</v>
       </c>
       <c r="B57" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C57" t="s">
         <v>80</v>
@@ -2544,16 +2544,16 @@
         <v>46225.47916666666</v>
       </c>
       <c r="E57" s="2">
-        <v>46225.5625</v>
+        <v>46225.60416666666</v>
       </c>
       <c r="F57" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G57">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H57">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -2564,7 +2564,7 @@
         <v>9</v>
       </c>
       <c r="B58" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C58" t="s">
         <v>81</v>
@@ -2573,16 +2573,16 @@
         <v>46225.70833333334</v>
       </c>
       <c r="E58" s="2">
-        <v>46225.83333333334</v>
+        <v>46225.77083333334</v>
       </c>
       <c r="F58" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G58">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H58">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -2602,16 +2602,16 @@
         <v>46225.70833333334</v>
       </c>
       <c r="E59" s="2">
-        <v>46225.77083333334</v>
+        <v>46225.79166666666</v>
       </c>
       <c r="F59" t="s">
         <v>171</v>
       </c>
       <c r="G59">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H59">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -2622,7 +2622,7 @@
         <v>9</v>
       </c>
       <c r="B60" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C60" t="s">
         <v>83</v>
@@ -2631,16 +2631,16 @@
         <v>46225.70833333334</v>
       </c>
       <c r="E60" s="2">
-        <v>46225.79166666666</v>
+        <v>46225.83333333334</v>
       </c>
       <c r="F60" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G60">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H60">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -2651,7 +2651,7 @@
         <v>9</v>
       </c>
       <c r="B61" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C61" t="s">
         <v>84</v>
@@ -2660,16 +2660,16 @@
         <v>46225.70833333334</v>
       </c>
       <c r="E61" s="2">
-        <v>46225.83333333334</v>
+        <v>46225.77083333334</v>
       </c>
       <c r="F61" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G61">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H61">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -2680,7 +2680,7 @@
         <v>9</v>
       </c>
       <c r="B62" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C62" t="s">
         <v>85</v>
@@ -2689,16 +2689,16 @@
         <v>46225.70833333334</v>
       </c>
       <c r="E62" s="2">
-        <v>46225.77083333334</v>
+        <v>46225.83333333334</v>
       </c>
       <c r="F62" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G62">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H62">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -2721,7 +2721,7 @@
         <v>46225.83333333334</v>
       </c>
       <c r="F63" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G63">
         <v>4</v>
@@ -2730,7 +2730,7 @@
         <v>17</v>
       </c>
       <c r="I63">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -2738,7 +2738,7 @@
         <v>9</v>
       </c>
       <c r="B64" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C64" t="s">
         <v>87</v>
@@ -2750,13 +2750,13 @@
         <v>46226.41666666666</v>
       </c>
       <c r="F64" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G64">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H64">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -2779,7 +2779,7 @@
         <v>46226.35416666666</v>
       </c>
       <c r="F65" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G65">
         <v>10</v>
@@ -2808,13 +2808,13 @@
         <v>46226.41666666666</v>
       </c>
       <c r="F66" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G66">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H66">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -2854,7 +2854,7 @@
         <v>9</v>
       </c>
       <c r="B68" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C68" t="s">
         <v>91</v>
@@ -2866,7 +2866,7 @@
         <v>46226.54166666666</v>
       </c>
       <c r="F68" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G68">
         <v>8</v>
@@ -2883,7 +2883,7 @@
         <v>9</v>
       </c>
       <c r="B69" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C69" t="s">
         <v>92</v>
@@ -2892,16 +2892,16 @@
         <v>46226.47916666666</v>
       </c>
       <c r="E69" s="2">
-        <v>46226.54166666666</v>
+        <v>46226.60416666666</v>
       </c>
       <c r="F69" t="s">
         <v>172</v>
       </c>
       <c r="G69">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H69">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -2912,7 +2912,7 @@
         <v>9</v>
       </c>
       <c r="B70" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C70" t="s">
         <v>93</v>
@@ -2921,16 +2921,16 @@
         <v>46226.47916666666</v>
       </c>
       <c r="E70" s="2">
-        <v>46226.60416666666</v>
+        <v>46226.5625</v>
       </c>
       <c r="F70" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G70">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H70">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>9</v>
       </c>
       <c r="B71" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C71" t="s">
         <v>94</v>
@@ -2950,16 +2950,16 @@
         <v>46226.47916666666</v>
       </c>
       <c r="E71" s="2">
-        <v>46226.5625</v>
+        <v>46226.54166666666</v>
       </c>
       <c r="F71" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G71">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H71">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -2970,7 +2970,7 @@
         <v>9</v>
       </c>
       <c r="B72" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C72" t="s">
         <v>95</v>
@@ -2982,7 +2982,7 @@
         <v>46226.60416666666</v>
       </c>
       <c r="F72" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G72">
         <v>7</v>
@@ -2999,7 +2999,7 @@
         <v>9</v>
       </c>
       <c r="B73" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C73" t="s">
         <v>96</v>
@@ -3011,7 +3011,7 @@
         <v>46226.83333333334</v>
       </c>
       <c r="F73" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G73">
         <v>1</v>
@@ -3040,7 +3040,7 @@
         <v>46226.77083333334</v>
       </c>
       <c r="F74" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G74">
         <v>4</v>
@@ -3057,7 +3057,7 @@
         <v>9</v>
       </c>
       <c r="B75" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C75" t="s">
         <v>98</v>
@@ -3069,7 +3069,7 @@
         <v>46226.83333333334</v>
       </c>
       <c r="F75" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G75">
         <v>7</v>
@@ -3098,7 +3098,7 @@
         <v>46226.83333333334</v>
       </c>
       <c r="F76" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G76">
         <v>4</v>
@@ -3124,16 +3124,16 @@
         <v>46227.29166666666</v>
       </c>
       <c r="E77" s="2">
-        <v>46227.39583333334</v>
+        <v>46227.41666666666</v>
       </c>
       <c r="F77" t="s">
         <v>172</v>
       </c>
       <c r="G77">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H77">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="I77">
         <v>0</v>
@@ -3156,7 +3156,7 @@
         <v>46227.35416666666</v>
       </c>
       <c r="F78" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G78">
         <v>10</v>
@@ -3185,16 +3185,16 @@
         <v>46227.41666666666</v>
       </c>
       <c r="F79" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G79">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H79">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I79">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -3214,13 +3214,13 @@
         <v>46227.39583333334</v>
       </c>
       <c r="F80" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G80">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H80">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I80">
         <v>0</v>
@@ -3240,16 +3240,16 @@
         <v>46227.29166666666</v>
       </c>
       <c r="E81" s="2">
-        <v>46227.41666666666</v>
+        <v>46227.39583333334</v>
       </c>
       <c r="F81" t="s">
         <v>171</v>
       </c>
       <c r="G81">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H81">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I81">
         <v>0</v>
@@ -3289,7 +3289,7 @@
         <v>9</v>
       </c>
       <c r="B83" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C83" t="s">
         <v>106</v>
@@ -3298,19 +3298,19 @@
         <v>46227.47916666666</v>
       </c>
       <c r="E83" s="2">
-        <v>46227.5625</v>
+        <v>46227.60416666666</v>
       </c>
       <c r="F83" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G83">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H83">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I83">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -3330,7 +3330,7 @@
         <v>46227.54166666666</v>
       </c>
       <c r="F84" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G84">
         <v>10</v>
@@ -3359,13 +3359,13 @@
         <v>46227.60416666666</v>
       </c>
       <c r="F85" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G85">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H85">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I85">
         <v>0</v>
@@ -3388,13 +3388,13 @@
         <v>46227.58333333334</v>
       </c>
       <c r="F86" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G86">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H86">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I86">
         <v>0</v>
@@ -3414,16 +3414,16 @@
         <v>46227.47916666666</v>
       </c>
       <c r="E87" s="2">
-        <v>46227.60416666666</v>
+        <v>46227.58333333334</v>
       </c>
       <c r="F87" t="s">
         <v>171</v>
       </c>
       <c r="G87">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H87">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I87">
         <v>0</v>
@@ -3434,7 +3434,7 @@
         <v>9</v>
       </c>
       <c r="B88" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C88" t="s">
         <v>111</v>
@@ -3443,16 +3443,16 @@
         <v>46227.47916666666</v>
       </c>
       <c r="E88" s="2">
-        <v>46227.58333333334</v>
+        <v>46227.54166666666</v>
       </c>
       <c r="F88" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G88">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H88">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I88">
         <v>0</v>
@@ -3472,16 +3472,16 @@
         <v>46227.47916666666</v>
       </c>
       <c r="E89" s="2">
-        <v>46227.54166666666</v>
+        <v>46227.5625</v>
       </c>
       <c r="F89" t="s">
         <v>171</v>
       </c>
       <c r="G89">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H89">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I89">
         <v>0</v>
@@ -3504,13 +3504,13 @@
         <v>46227.83333333334</v>
       </c>
       <c r="F90" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G90">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H90">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I90">
         <v>0</v>
@@ -3521,7 +3521,7 @@
         <v>9</v>
       </c>
       <c r="B91" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C91" t="s">
         <v>114</v>
@@ -3530,16 +3530,16 @@
         <v>46227.70833333334</v>
       </c>
       <c r="E91" s="2">
-        <v>46227.83333333334</v>
+        <v>46227.77083333334</v>
       </c>
       <c r="F91" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G91">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H91">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I91">
         <v>0</v>
@@ -3550,7 +3550,7 @@
         <v>9</v>
       </c>
       <c r="B92" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C92" t="s">
         <v>115</v>
@@ -3559,16 +3559,16 @@
         <v>46227.70833333334</v>
       </c>
       <c r="E92" s="2">
-        <v>46227.77083333334</v>
+        <v>46227.83333333334</v>
       </c>
       <c r="F92" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G92">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H92">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I92">
         <v>0</v>
@@ -3591,7 +3591,7 @@
         <v>46227.83333333334</v>
       </c>
       <c r="F93" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G93">
         <v>4</v>
@@ -3608,7 +3608,7 @@
         <v>9</v>
       </c>
       <c r="B94" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C94" t="s">
         <v>117</v>
@@ -3617,16 +3617,16 @@
         <v>46228.29166666666</v>
       </c>
       <c r="E94" s="2">
-        <v>46228.375</v>
+        <v>46228.41666666666</v>
       </c>
       <c r="F94" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G94">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H94">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I94">
         <v>0</v>
@@ -3637,7 +3637,7 @@
         <v>9</v>
       </c>
       <c r="B95" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C95" t="s">
         <v>118</v>
@@ -3646,16 +3646,16 @@
         <v>46228.29166666666</v>
       </c>
       <c r="E95" s="2">
-        <v>46228.41666666666</v>
+        <v>46228.39583333334</v>
       </c>
       <c r="F95" t="s">
         <v>173</v>
       </c>
       <c r="G95">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H95">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I95">
         <v>0</v>
@@ -3666,7 +3666,7 @@
         <v>9</v>
       </c>
       <c r="B96" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C96" t="s">
         <v>119</v>
@@ -3678,7 +3678,7 @@
         <v>46228.39583333334</v>
       </c>
       <c r="F96" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G96">
         <v>5</v>
@@ -3695,7 +3695,7 @@
         <v>9</v>
       </c>
       <c r="B97" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C97" t="s">
         <v>120</v>
@@ -3707,13 +3707,13 @@
         <v>46228.41666666666</v>
       </c>
       <c r="F97" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G97">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H97">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I97">
         <v>0</v>
@@ -3724,7 +3724,7 @@
         <v>9</v>
       </c>
       <c r="B98" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C98" t="s">
         <v>121</v>
@@ -3733,16 +3733,16 @@
         <v>46228.29166666666</v>
       </c>
       <c r="E98" s="2">
-        <v>46228.39583333334</v>
+        <v>46228.375</v>
       </c>
       <c r="F98" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G98">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H98">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I98">
         <v>0</v>
@@ -3765,7 +3765,7 @@
         <v>46228.35416666666</v>
       </c>
       <c r="F99" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G99">
         <v>10</v>
@@ -3782,7 +3782,7 @@
         <v>9</v>
       </c>
       <c r="B100" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C100" t="s">
         <v>123</v>
@@ -3791,19 +3791,19 @@
         <v>46228.47916666666</v>
       </c>
       <c r="E100" s="2">
-        <v>46228.5625</v>
+        <v>46228.60416666666</v>
       </c>
       <c r="F100" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G100">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H100">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I100">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:9">
@@ -3823,13 +3823,13 @@
         <v>46228.58333333334</v>
       </c>
       <c r="F101" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G101">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H101">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I101">
         <v>0</v>
@@ -3849,19 +3849,19 @@
         <v>46228.47916666666</v>
       </c>
       <c r="E102" s="2">
-        <v>46228.60416666666</v>
+        <v>46228.58333333334</v>
       </c>
       <c r="F102" t="s">
         <v>171</v>
       </c>
       <c r="G102">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H102">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I102">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -3878,16 +3878,16 @@
         <v>46228.47916666666</v>
       </c>
       <c r="E103" s="2">
-        <v>46228.58333333334</v>
+        <v>46228.60416666666</v>
       </c>
       <c r="F103" t="s">
         <v>172</v>
       </c>
       <c r="G103">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H103">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="I103">
         <v>0</v>
@@ -3898,7 +3898,7 @@
         <v>9</v>
       </c>
       <c r="B104" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C104" t="s">
         <v>127</v>
@@ -3907,16 +3907,16 @@
         <v>46228.47916666666</v>
       </c>
       <c r="E104" s="2">
-        <v>46228.54166666666</v>
+        <v>46228.5625</v>
       </c>
       <c r="F104" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G104">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H104">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="I104">
         <v>0</v>
@@ -3927,7 +3927,7 @@
         <v>9</v>
       </c>
       <c r="B105" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C105" t="s">
         <v>128</v>
@@ -3936,16 +3936,16 @@
         <v>46228.47916666666</v>
       </c>
       <c r="E105" s="2">
-        <v>46228.60416666666</v>
+        <v>46228.54166666666</v>
       </c>
       <c r="F105" t="s">
         <v>173</v>
       </c>
       <c r="G105">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H105">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="I105">
         <v>0</v>
@@ -3956,25 +3956,25 @@
         <v>10</v>
       </c>
       <c r="B106" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C106" t="s">
-        <v>129</v>
+        <v>27</v>
       </c>
       <c r="D106" s="2">
         <v>46222.29166666666</v>
       </c>
       <c r="E106" s="2">
-        <v>46222.41666666666</v>
+        <v>46222.35416666666</v>
       </c>
       <c r="F106" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G106">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H106">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I106">
         <v>0</v>
@@ -3985,28 +3985,28 @@
         <v>10</v>
       </c>
       <c r="B107" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C107" t="s">
-        <v>27</v>
+        <v>129</v>
       </c>
       <c r="D107" s="2">
         <v>46222.29166666666</v>
       </c>
       <c r="E107" s="2">
-        <v>46222.35416666666</v>
+        <v>46222.41666666666</v>
       </c>
       <c r="F107" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G107">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H107">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I107">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -4014,25 +4014,25 @@
         <v>10</v>
       </c>
       <c r="B108" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C108" t="s">
-        <v>130</v>
+        <v>32</v>
       </c>
       <c r="D108" s="2">
         <v>46222.47916666666</v>
       </c>
       <c r="E108" s="2">
-        <v>46222.60416666666</v>
+        <v>46222.54166666666</v>
       </c>
       <c r="F108" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G108">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H108">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I108">
         <v>0</v>
@@ -4043,25 +4043,25 @@
         <v>10</v>
       </c>
       <c r="B109" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C109" t="s">
-        <v>31</v>
+        <v>130</v>
       </c>
       <c r="D109" s="2">
         <v>46222.47916666666</v>
       </c>
       <c r="E109" s="2">
-        <v>46222.54166666666</v>
+        <v>46222.60416666666</v>
       </c>
       <c r="F109" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G109">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H109">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I109">
         <v>0</v>
@@ -4084,7 +4084,7 @@
         <v>46223.41666666666</v>
       </c>
       <c r="F110" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G110">
         <v>8</v>
@@ -4130,25 +4130,25 @@
         <v>10</v>
       </c>
       <c r="B112" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C112" t="s">
-        <v>39</v>
+        <v>132</v>
       </c>
       <c r="D112" s="2">
         <v>46223.47916666666</v>
       </c>
       <c r="E112" s="2">
-        <v>46223.5625</v>
+        <v>46223.60416666666</v>
       </c>
       <c r="F112" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G112">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H112">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="I112">
         <v>0</v>
@@ -4162,22 +4162,22 @@
         <v>18</v>
       </c>
       <c r="C113" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D113" s="2">
         <v>46223.47916666666</v>
       </c>
       <c r="E113" s="2">
-        <v>46223.54166666666</v>
+        <v>46223.5625</v>
       </c>
       <c r="F113" t="s">
         <v>171</v>
       </c>
       <c r="G113">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H113">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I113">
         <v>0</v>
@@ -4188,10 +4188,10 @@
         <v>10</v>
       </c>
       <c r="B114" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C114" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D114" s="2">
         <v>46223.47916666666</v>
@@ -4203,13 +4203,13 @@
         <v>174</v>
       </c>
       <c r="G114">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H114">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="I114">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -4217,25 +4217,25 @@
         <v>10</v>
       </c>
       <c r="B115" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C115" t="s">
-        <v>133</v>
+        <v>40</v>
       </c>
       <c r="D115" s="2">
         <v>46223.47916666666</v>
       </c>
       <c r="E115" s="2">
-        <v>46223.60416666666</v>
+        <v>46223.54166666666</v>
       </c>
       <c r="F115" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G115">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H115">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I115">
         <v>0</v>
@@ -4246,25 +4246,25 @@
         <v>10</v>
       </c>
       <c r="B116" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C116" t="s">
-        <v>134</v>
+        <v>47</v>
       </c>
       <c r="D116" s="2">
         <v>46223.70833333334</v>
       </c>
       <c r="E116" s="2">
-        <v>46223.83333333334</v>
+        <v>46223.79166666666</v>
       </c>
       <c r="F116" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G116">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H116">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="I116">
         <v>0</v>
@@ -4275,25 +4275,25 @@
         <v>10</v>
       </c>
       <c r="B117" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C117" t="s">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="D117" s="2">
         <v>46223.70833333334</v>
       </c>
       <c r="E117" s="2">
-        <v>46223.77083333334</v>
+        <v>46223.83333333334</v>
       </c>
       <c r="F117" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G117">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H117">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I117">
         <v>0</v>
@@ -4304,7 +4304,7 @@
         <v>10</v>
       </c>
       <c r="B118" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C118" t="s">
         <v>135</v>
@@ -4313,16 +4313,16 @@
         <v>46223.70833333334</v>
       </c>
       <c r="E118" s="2">
-        <v>46223.75</v>
+        <v>46223.83333333334</v>
       </c>
       <c r="F118" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G118">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H118">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I118">
         <v>0</v>
@@ -4333,25 +4333,25 @@
         <v>10</v>
       </c>
       <c r="B119" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C119" t="s">
-        <v>136</v>
+        <v>48</v>
       </c>
       <c r="D119" s="2">
         <v>46223.70833333334</v>
       </c>
       <c r="E119" s="2">
-        <v>46223.83333333334</v>
+        <v>46223.77083333334</v>
       </c>
       <c r="F119" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G119">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H119">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I119">
         <v>0</v>
@@ -4365,7 +4365,7 @@
         <v>19</v>
       </c>
       <c r="C120" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D120" s="2">
         <v>46223.70833333334</v>
@@ -4374,7 +4374,7 @@
         <v>46223.77083333334</v>
       </c>
       <c r="F120" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G120">
         <v>9</v>
@@ -4391,10 +4391,10 @@
         <v>10</v>
       </c>
       <c r="B121" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C121" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D121" s="2">
         <v>46223.70833333334</v>
@@ -4403,13 +4403,13 @@
         <v>46223.75</v>
       </c>
       <c r="F121" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G121">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H121">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I121">
         <v>0</v>
@@ -4420,25 +4420,25 @@
         <v>10</v>
       </c>
       <c r="B122" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C122" t="s">
-        <v>47</v>
+        <v>137</v>
       </c>
       <c r="D122" s="2">
         <v>46223.70833333334</v>
       </c>
       <c r="E122" s="2">
-        <v>46223.79166666666</v>
+        <v>46223.75</v>
       </c>
       <c r="F122" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G122">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H122">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="I122">
         <v>0</v>
@@ -4449,25 +4449,25 @@
         <v>10</v>
       </c>
       <c r="B123" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C123" t="s">
-        <v>138</v>
+        <v>49</v>
       </c>
       <c r="D123" s="2">
         <v>46223.77083333334</v>
       </c>
       <c r="E123" s="2">
-        <v>46223.8125</v>
+        <v>46223.83333333334</v>
       </c>
       <c r="F123" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G123">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H123">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I123">
         <v>0</v>
@@ -4478,28 +4478,28 @@
         <v>10</v>
       </c>
       <c r="B124" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C124" t="s">
-        <v>49</v>
+        <v>138</v>
       </c>
       <c r="D124" s="2">
         <v>46223.77083333334</v>
       </c>
       <c r="E124" s="2">
-        <v>46223.83333333334</v>
+        <v>46223.8125</v>
       </c>
       <c r="F124" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G124">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H124">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I124">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:9">
@@ -4519,7 +4519,7 @@
         <v>46224.41666666666</v>
       </c>
       <c r="F125" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G125">
         <v>8</v>
@@ -4528,7 +4528,7 @@
         <v>13</v>
       </c>
       <c r="I125">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126" spans="1:9">
@@ -4565,25 +4565,25 @@
         <v>10</v>
       </c>
       <c r="B127" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C127" t="s">
-        <v>58</v>
+        <v>140</v>
       </c>
       <c r="D127" s="2">
         <v>46224.47916666666</v>
       </c>
       <c r="E127" s="2">
-        <v>46224.54166666666</v>
+        <v>46224.60416666666</v>
       </c>
       <c r="F127" t="s">
         <v>171</v>
       </c>
       <c r="G127">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H127">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I127">
         <v>0</v>
@@ -4594,25 +4594,25 @@
         <v>10</v>
       </c>
       <c r="B128" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C128" t="s">
-        <v>140</v>
+        <v>61</v>
       </c>
       <c r="D128" s="2">
         <v>46224.47916666666</v>
       </c>
       <c r="E128" s="2">
-        <v>46224.60416666666</v>
+        <v>46224.5625</v>
       </c>
       <c r="F128" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G128">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H128">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="I128">
         <v>0</v>
@@ -4623,25 +4623,25 @@
         <v>10</v>
       </c>
       <c r="B129" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C129" t="s">
-        <v>62</v>
+        <v>141</v>
       </c>
       <c r="D129" s="2">
         <v>46224.47916666666</v>
       </c>
       <c r="E129" s="2">
-        <v>46224.5625</v>
+        <v>46224.60416666666</v>
       </c>
       <c r="F129" t="s">
         <v>174</v>
       </c>
       <c r="G129">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H129">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I129">
         <v>0</v>
@@ -4652,28 +4652,28 @@
         <v>10</v>
       </c>
       <c r="B130" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C130" t="s">
-        <v>141</v>
+        <v>57</v>
       </c>
       <c r="D130" s="2">
         <v>46224.47916666666</v>
       </c>
       <c r="E130" s="2">
-        <v>46224.60416666666</v>
+        <v>46224.54166666666</v>
       </c>
       <c r="F130" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G130">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H130">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I130">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131" spans="1:9">
@@ -4681,28 +4681,28 @@
         <v>10</v>
       </c>
       <c r="B131" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C131" t="s">
-        <v>142</v>
+        <v>65</v>
       </c>
       <c r="D131" s="2">
         <v>46224.70833333334</v>
       </c>
       <c r="E131" s="2">
-        <v>46224.75</v>
+        <v>46224.77083333334</v>
       </c>
       <c r="F131" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G131">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H131">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I131">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:9">
@@ -4710,25 +4710,25 @@
         <v>10</v>
       </c>
       <c r="B132" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C132" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D132" s="2">
         <v>46224.70833333334</v>
       </c>
       <c r="E132" s="2">
-        <v>46224.79166666666</v>
+        <v>46224.75</v>
       </c>
       <c r="F132" t="s">
         <v>174</v>
       </c>
       <c r="G132">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H132">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I132">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>10</v>
       </c>
       <c r="B133" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C133" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D133" s="2">
         <v>46224.70833333334</v>
@@ -4754,10 +4754,10 @@
         <v>174</v>
       </c>
       <c r="G133">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H133">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="I133">
         <v>0</v>
@@ -4768,25 +4768,25 @@
         <v>10</v>
       </c>
       <c r="B134" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C134" t="s">
-        <v>144</v>
+        <v>63</v>
       </c>
       <c r="D134" s="2">
         <v>46224.70833333334</v>
       </c>
       <c r="E134" s="2">
-        <v>46224.75</v>
+        <v>46224.79166666666</v>
       </c>
       <c r="F134" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G134">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H134">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="I134">
         <v>0</v>
@@ -4797,10 +4797,10 @@
         <v>10</v>
       </c>
       <c r="B135" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C135" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D135" s="2">
         <v>46224.70833333334</v>
@@ -4812,10 +4812,10 @@
         <v>171</v>
       </c>
       <c r="G135">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H135">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I135">
         <v>0</v>
@@ -4826,25 +4826,25 @@
         <v>10</v>
       </c>
       <c r="B136" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C136" t="s">
-        <v>66</v>
+        <v>144</v>
       </c>
       <c r="D136" s="2">
         <v>46224.70833333334</v>
       </c>
       <c r="E136" s="2">
-        <v>46224.77083333334</v>
+        <v>46224.75</v>
       </c>
       <c r="F136" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G136">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H136">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I136">
         <v>0</v>
@@ -4855,10 +4855,10 @@
         <v>10</v>
       </c>
       <c r="B137" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C137" t="s">
-        <v>67</v>
+        <v>145</v>
       </c>
       <c r="D137" s="2">
         <v>46224.70833333334</v>
@@ -4870,10 +4870,10 @@
         <v>171</v>
       </c>
       <c r="G137">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H137">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I137">
         <v>0</v>
@@ -4896,7 +4896,7 @@
         <v>46224.83333333334</v>
       </c>
       <c r="F138" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G138">
         <v>9</v>
@@ -4925,7 +4925,7 @@
         <v>46224.8125</v>
       </c>
       <c r="F139" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G139">
         <v>3</v>
@@ -4942,28 +4942,28 @@
         <v>10</v>
       </c>
       <c r="B140" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C140" t="s">
-        <v>147</v>
+        <v>71</v>
       </c>
       <c r="D140" s="2">
         <v>46225.29166666666</v>
       </c>
       <c r="E140" s="2">
-        <v>46225.41666666666</v>
+        <v>46225.35416666666</v>
       </c>
       <c r="F140" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G140">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H140">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I140">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141" spans="1:9">
@@ -4971,25 +4971,25 @@
         <v>10</v>
       </c>
       <c r="B141" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C141" t="s">
-        <v>69</v>
+        <v>147</v>
       </c>
       <c r="D141" s="2">
         <v>46225.29166666666</v>
       </c>
       <c r="E141" s="2">
-        <v>46225.35416666666</v>
+        <v>46225.41666666666</v>
       </c>
       <c r="F141" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G141">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H141">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I141">
         <v>0</v>
@@ -5000,25 +5000,25 @@
         <v>10</v>
       </c>
       <c r="B142" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C142" t="s">
-        <v>148</v>
+        <v>75</v>
       </c>
       <c r="D142" s="2">
         <v>46225.47916666666</v>
       </c>
       <c r="E142" s="2">
-        <v>46225.60416666666</v>
+        <v>46225.54166666666</v>
       </c>
       <c r="F142" t="s">
         <v>174</v>
       </c>
       <c r="G142">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H142">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I142">
         <v>0</v>
@@ -5032,22 +5032,22 @@
         <v>18</v>
       </c>
       <c r="C143" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D143" s="2">
         <v>46225.47916666666</v>
       </c>
       <c r="E143" s="2">
-        <v>46225.54166666666</v>
+        <v>46225.5625</v>
       </c>
       <c r="F143" t="s">
         <v>171</v>
       </c>
       <c r="G143">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H143">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I143">
         <v>0</v>
@@ -5058,25 +5058,25 @@
         <v>10</v>
       </c>
       <c r="B144" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C144" t="s">
-        <v>149</v>
+        <v>79</v>
       </c>
       <c r="D144" s="2">
         <v>46225.47916666666</v>
       </c>
       <c r="E144" s="2">
-        <v>46225.60416666666</v>
+        <v>46225.54166666666</v>
       </c>
       <c r="F144" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G144">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H144">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I144">
         <v>0</v>
@@ -5087,25 +5087,25 @@
         <v>10</v>
       </c>
       <c r="B145" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C145" t="s">
-        <v>78</v>
+        <v>148</v>
       </c>
       <c r="D145" s="2">
         <v>46225.47916666666</v>
       </c>
       <c r="E145" s="2">
-        <v>46225.54166666666</v>
+        <v>46225.60416666666</v>
       </c>
       <c r="F145" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G145">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H145">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I145">
         <v>0</v>
@@ -5116,25 +5116,25 @@
         <v>10</v>
       </c>
       <c r="B146" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C146" t="s">
-        <v>74</v>
+        <v>149</v>
       </c>
       <c r="D146" s="2">
         <v>46225.47916666666</v>
       </c>
       <c r="E146" s="2">
-        <v>46225.5625</v>
+        <v>46225.60416666666</v>
       </c>
       <c r="F146" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G146">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H146">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="I146">
         <v>0</v>
@@ -5145,7 +5145,7 @@
         <v>10</v>
       </c>
       <c r="B147" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C147" t="s">
         <v>150</v>
@@ -5154,16 +5154,16 @@
         <v>46225.70833333334</v>
       </c>
       <c r="E147" s="2">
-        <v>46225.83333333334</v>
+        <v>46225.75</v>
       </c>
       <c r="F147" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G147">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H147">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I147">
         <v>0</v>
@@ -5174,25 +5174,25 @@
         <v>10</v>
       </c>
       <c r="B148" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C148" t="s">
-        <v>151</v>
+        <v>84</v>
       </c>
       <c r="D148" s="2">
         <v>46225.70833333334</v>
       </c>
       <c r="E148" s="2">
-        <v>46225.75</v>
+        <v>46225.77083333334</v>
       </c>
       <c r="F148" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G148">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H148">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I148">
         <v>0</v>
@@ -5203,25 +5203,25 @@
         <v>10</v>
       </c>
       <c r="B149" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C149" t="s">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="D149" s="2">
         <v>46225.70833333334</v>
       </c>
       <c r="E149" s="2">
-        <v>46225.77083333334</v>
+        <v>46225.75</v>
       </c>
       <c r="F149" t="s">
         <v>171</v>
       </c>
       <c r="G149">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H149">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I149">
         <v>0</v>
@@ -5232,25 +5232,25 @@
         <v>10</v>
       </c>
       <c r="B150" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C150" t="s">
-        <v>83</v>
+        <v>152</v>
       </c>
       <c r="D150" s="2">
         <v>46225.70833333334</v>
       </c>
       <c r="E150" s="2">
-        <v>46225.79166666666</v>
+        <v>46225.83333333334</v>
       </c>
       <c r="F150" t="s">
         <v>174</v>
       </c>
       <c r="G150">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H150">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I150">
         <v>0</v>
@@ -5261,28 +5261,28 @@
         <v>10</v>
       </c>
       <c r="B151" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C151" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D151" s="2">
         <v>46225.70833333334</v>
       </c>
       <c r="E151" s="2">
-        <v>46225.75</v>
+        <v>46225.83333333334</v>
       </c>
       <c r="F151" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G151">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H151">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I151">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:9">
@@ -5290,25 +5290,25 @@
         <v>10</v>
       </c>
       <c r="B152" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C152" t="s">
-        <v>153</v>
+        <v>81</v>
       </c>
       <c r="D152" s="2">
         <v>46225.70833333334</v>
       </c>
       <c r="E152" s="2">
-        <v>46225.83333333334</v>
+        <v>46225.77083333334</v>
       </c>
       <c r="F152" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G152">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H152">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I152">
         <v>0</v>
@@ -5319,25 +5319,25 @@
         <v>10</v>
       </c>
       <c r="B153" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C153" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D153" s="2">
         <v>46225.70833333334</v>
       </c>
       <c r="E153" s="2">
-        <v>46225.77083333334</v>
+        <v>46225.79166666666</v>
       </c>
       <c r="F153" t="s">
         <v>171</v>
       </c>
       <c r="G153">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H153">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I153">
         <v>0</v>
@@ -5360,7 +5360,7 @@
         <v>46225.8125</v>
       </c>
       <c r="F154" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G154">
         <v>3</v>
@@ -5389,7 +5389,7 @@
         <v>46225.83333333334</v>
       </c>
       <c r="F155" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G155">
         <v>9</v>
@@ -5406,25 +5406,25 @@
         <v>10</v>
       </c>
       <c r="B156" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C156" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="D156" s="2">
         <v>46226.29166666666</v>
       </c>
       <c r="E156" s="2">
-        <v>46226.41666666666</v>
+        <v>46226.35416666666</v>
       </c>
       <c r="F156" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G156">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H156">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I156">
         <v>0</v>
@@ -5435,25 +5435,25 @@
         <v>10</v>
       </c>
       <c r="B157" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C157" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="D157" s="2">
         <v>46226.29166666666</v>
       </c>
       <c r="E157" s="2">
-        <v>46226.35416666666</v>
+        <v>46226.41666666666</v>
       </c>
       <c r="F157" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G157">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H157">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I157">
         <v>0</v>
@@ -5493,25 +5493,25 @@
         <v>10</v>
       </c>
       <c r="B159" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C159" t="s">
-        <v>156</v>
+        <v>93</v>
       </c>
       <c r="D159" s="2">
         <v>46226.47916666666</v>
       </c>
       <c r="E159" s="2">
-        <v>46226.60416666666</v>
+        <v>46226.5625</v>
       </c>
       <c r="F159" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G159">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H159">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="I159">
         <v>0</v>
@@ -5522,10 +5522,10 @@
         <v>10</v>
       </c>
       <c r="B160" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C160" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D160" s="2">
         <v>46226.47916666666</v>
@@ -5534,16 +5534,16 @@
         <v>46226.54166666666</v>
       </c>
       <c r="F160" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G160">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H160">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I160">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161" spans="1:9">
@@ -5554,7 +5554,7 @@
         <v>21</v>
       </c>
       <c r="C161" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D161" s="2">
         <v>46226.47916666666</v>
@@ -5563,7 +5563,7 @@
         <v>46226.60416666666</v>
       </c>
       <c r="F161" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G161">
         <v>8</v>
@@ -5580,28 +5580,28 @@
         <v>10</v>
       </c>
       <c r="B162" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C162" t="s">
-        <v>92</v>
+        <v>157</v>
       </c>
       <c r="D162" s="2">
         <v>46226.47916666666</v>
       </c>
       <c r="E162" s="2">
-        <v>46226.54166666666</v>
+        <v>46226.60416666666</v>
       </c>
       <c r="F162" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G162">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H162">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I162">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="163" spans="1:9">
@@ -5612,22 +5612,22 @@
         <v>17</v>
       </c>
       <c r="C163" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D163" s="2">
         <v>46226.47916666666</v>
       </c>
       <c r="E163" s="2">
-        <v>46226.5625</v>
+        <v>46226.54166666666</v>
       </c>
       <c r="F163" t="s">
         <v>174</v>
       </c>
       <c r="G163">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H163">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I163">
         <v>0</v>
@@ -5638,7 +5638,7 @@
         <v>10</v>
       </c>
       <c r="B164" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C164" t="s">
         <v>158</v>
@@ -5650,13 +5650,13 @@
         <v>46226.75</v>
       </c>
       <c r="F164" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G164">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H164">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I164">
         <v>0</v>
@@ -5667,28 +5667,28 @@
         <v>10</v>
       </c>
       <c r="B165" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C165" t="s">
-        <v>159</v>
+        <v>97</v>
       </c>
       <c r="D165" s="2">
         <v>46226.70833333334</v>
       </c>
       <c r="E165" s="2">
-        <v>46226.83333333334</v>
+        <v>46226.77083333334</v>
       </c>
       <c r="F165" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G165">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H165">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I165">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166" spans="1:9">
@@ -5696,28 +5696,28 @@
         <v>10</v>
       </c>
       <c r="B166" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C166" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="D166" s="2">
         <v>46226.70833333334</v>
       </c>
       <c r="E166" s="2">
-        <v>46226.77083333334</v>
+        <v>46226.75</v>
       </c>
       <c r="F166" t="s">
         <v>171</v>
       </c>
       <c r="G166">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H166">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I166">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="167" spans="1:9">
@@ -5725,7 +5725,7 @@
         <v>10</v>
       </c>
       <c r="B167" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C167" t="s">
         <v>160</v>
@@ -5734,16 +5734,16 @@
         <v>46226.70833333334</v>
       </c>
       <c r="E167" s="2">
-        <v>46226.75</v>
+        <v>46226.83333333334</v>
       </c>
       <c r="F167" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G167">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H167">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="I167">
         <v>0</v>
@@ -5754,25 +5754,25 @@
         <v>10</v>
       </c>
       <c r="B168" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C168" t="s">
-        <v>161</v>
+        <v>99</v>
       </c>
       <c r="D168" s="2">
         <v>46226.77083333334</v>
       </c>
       <c r="E168" s="2">
-        <v>46226.8125</v>
+        <v>46226.83333333334</v>
       </c>
       <c r="F168" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G168">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H168">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I168">
         <v>0</v>
@@ -5783,25 +5783,25 @@
         <v>10</v>
       </c>
       <c r="B169" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C169" t="s">
-        <v>99</v>
+        <v>161</v>
       </c>
       <c r="D169" s="2">
         <v>46226.77083333334</v>
       </c>
       <c r="E169" s="2">
-        <v>46226.83333333334</v>
+        <v>46226.8125</v>
       </c>
       <c r="F169" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G169">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H169">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I169">
         <v>0</v>
@@ -5812,25 +5812,25 @@
         <v>10</v>
       </c>
       <c r="B170" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C170" t="s">
-        <v>162</v>
+        <v>101</v>
       </c>
       <c r="D170" s="2">
         <v>46227.29166666666</v>
       </c>
       <c r="E170" s="2">
-        <v>46227.41666666666</v>
+        <v>46227.35416666666</v>
       </c>
       <c r="F170" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G170">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H170">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I170">
         <v>0</v>
@@ -5841,25 +5841,25 @@
         <v>10</v>
       </c>
       <c r="B171" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C171" t="s">
-        <v>101</v>
+        <v>162</v>
       </c>
       <c r="D171" s="2">
         <v>46227.29166666666</v>
       </c>
       <c r="E171" s="2">
-        <v>46227.35416666666</v>
+        <v>46227.41666666666</v>
       </c>
       <c r="F171" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G171">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H171">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I171">
         <v>0</v>
@@ -5899,25 +5899,25 @@
         <v>10</v>
       </c>
       <c r="B173" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C173" t="s">
-        <v>106</v>
+        <v>163</v>
       </c>
       <c r="D173" s="2">
         <v>46227.47916666666</v>
       </c>
       <c r="E173" s="2">
-        <v>46227.5625</v>
+        <v>46227.60416666666</v>
       </c>
       <c r="F173" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G173">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H173">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="I173">
         <v>0</v>
@@ -5928,25 +5928,25 @@
         <v>10</v>
       </c>
       <c r="B174" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C174" t="s">
-        <v>163</v>
+        <v>111</v>
       </c>
       <c r="D174" s="2">
         <v>46227.47916666666</v>
       </c>
       <c r="E174" s="2">
-        <v>46227.60416666666</v>
+        <v>46227.54166666666</v>
       </c>
       <c r="F174" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G174">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H174">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I174">
         <v>0</v>
@@ -5957,25 +5957,25 @@
         <v>10</v>
       </c>
       <c r="B175" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C175" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D175" s="2">
         <v>46227.47916666666</v>
       </c>
       <c r="E175" s="2">
-        <v>46227.54166666666</v>
+        <v>46227.5625</v>
       </c>
       <c r="F175" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G175">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H175">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I175">
         <v>0</v>
@@ -5986,25 +5986,25 @@
         <v>10</v>
       </c>
       <c r="B176" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C176" t="s">
-        <v>164</v>
+        <v>107</v>
       </c>
       <c r="D176" s="2">
         <v>46227.47916666666</v>
       </c>
       <c r="E176" s="2">
-        <v>46227.60416666666</v>
+        <v>46227.54166666666</v>
       </c>
       <c r="F176" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G176">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H176">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I176">
         <v>0</v>
@@ -6015,25 +6015,25 @@
         <v>10</v>
       </c>
       <c r="B177" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C177" t="s">
-        <v>112</v>
+        <v>164</v>
       </c>
       <c r="D177" s="2">
         <v>46227.47916666666</v>
       </c>
       <c r="E177" s="2">
-        <v>46227.54166666666</v>
+        <v>46227.60416666666</v>
       </c>
       <c r="F177" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G177">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H177">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I177">
         <v>0</v>
@@ -6044,25 +6044,25 @@
         <v>10</v>
       </c>
       <c r="B178" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C178" t="s">
-        <v>165</v>
+        <v>114</v>
       </c>
       <c r="D178" s="2">
         <v>46227.70833333334</v>
       </c>
       <c r="E178" s="2">
-        <v>46227.75</v>
+        <v>46227.77083333334</v>
       </c>
       <c r="F178" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G178">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H178">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I178">
         <v>0</v>
@@ -6073,25 +6073,25 @@
         <v>10</v>
       </c>
       <c r="B179" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C179" t="s">
-        <v>115</v>
+        <v>165</v>
       </c>
       <c r="D179" s="2">
         <v>46227.70833333334</v>
       </c>
       <c r="E179" s="2">
-        <v>46227.77083333334</v>
+        <v>46227.75</v>
       </c>
       <c r="F179" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G179">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H179">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I179">
         <v>0</v>
@@ -6114,7 +6114,7 @@
         <v>46227.75</v>
       </c>
       <c r="F180" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G180">
         <v>2</v>
@@ -6143,7 +6143,7 @@
         <v>46227.83333333334</v>
       </c>
       <c r="F181" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G181">
         <v>8</v>
@@ -6172,7 +6172,7 @@
         <v>46227.8125</v>
       </c>
       <c r="F182" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G182">
         <v>3</v>
@@ -6201,7 +6201,7 @@
         <v>46227.83333333334</v>
       </c>
       <c r="F183" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G183">
         <v>9</v>
@@ -6230,7 +6230,7 @@
         <v>46228.35416666666</v>
       </c>
       <c r="F184" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G184">
         <v>4</v>
@@ -6259,7 +6259,7 @@
         <v>46228.41666666666</v>
       </c>
       <c r="F185" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G185">
         <v>8</v>
@@ -6276,25 +6276,25 @@
         <v>10</v>
       </c>
       <c r="B186" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C186" t="s">
-        <v>170</v>
+        <v>128</v>
       </c>
       <c r="D186" s="2">
         <v>46228.47916666666</v>
       </c>
       <c r="E186" s="2">
-        <v>46228.60416666666</v>
+        <v>46228.54166666666</v>
       </c>
       <c r="F186" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G186">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H186">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I186">
         <v>0</v>
@@ -6305,25 +6305,25 @@
         <v>10</v>
       </c>
       <c r="B187" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C187" t="s">
-        <v>127</v>
+        <v>170</v>
       </c>
       <c r="D187" s="2">
         <v>46228.47916666666</v>
       </c>
       <c r="E187" s="2">
-        <v>46228.54166666666</v>
+        <v>46228.60416666666</v>
       </c>
       <c r="F187" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G187">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H187">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I187">
         <v>0</v>
